--- a/artfynd/A 15917-2024 artfynd.xlsx
+++ b/artfynd/A 15917-2024 artfynd.xlsx
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117451125</v>
+        <v>117451830</v>
       </c>
       <c r="B4" t="n">
-        <v>91772</v>
+        <v>97836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,41 +908,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn (Kurlberget/Ramptjärn), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516598</v>
+        <v>516845</v>
       </c>
       <c r="R4" t="n">
-        <v>6691837</v>
+        <v>6691943</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,11 +976,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,7 +1002,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117451153</v>
+        <v>117452372</v>
       </c>
       <c r="B5" t="n">
         <v>97753</v>
@@ -1043,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516596</v>
+        <v>516903</v>
       </c>
       <c r="R5" t="n">
-        <v>6691840</v>
+        <v>6691884</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1105,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117452372</v>
+        <v>117451892</v>
       </c>
       <c r="B6" t="n">
-        <v>97753</v>
+        <v>97836</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,38 +1116,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn (Kurlberget/Ramptjärn), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516903</v>
+        <v>516843</v>
       </c>
       <c r="R6" t="n">
-        <v>6691884</v>
+        <v>6691994</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1207,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117451335</v>
+        <v>117452042</v>
       </c>
       <c r="B7" t="n">
-        <v>78514</v>
+        <v>97753</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1247,13 +1250,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516633</v>
+        <v>516837</v>
       </c>
       <c r="R7" t="n">
-        <v>6691860</v>
+        <v>6691989</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117452042</v>
+        <v>117451435</v>
       </c>
       <c r="B8" t="n">
-        <v>97753</v>
+        <v>56499</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,37 +1328,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn (Kurlberget/Ramptjärn), Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516837</v>
+        <v>516620</v>
       </c>
       <c r="R8" t="n">
-        <v>6691989</v>
+        <v>6691868</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1411,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117451830</v>
+        <v>117451335</v>
       </c>
       <c r="B9" t="n">
-        <v>97836</v>
+        <v>78514</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,42 +1431,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn (Kurlberget/Ramptjärn), Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516845</v>
+        <v>516633</v>
       </c>
       <c r="R9" t="n">
-        <v>6691943</v>
+        <v>6691860</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1517,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117452199</v>
+        <v>117451125</v>
       </c>
       <c r="B10" t="n">
-        <v>97753</v>
+        <v>91772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,13 +1561,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516911</v>
+        <v>516598</v>
       </c>
       <c r="R10" t="n">
-        <v>6691957</v>
+        <v>6691837</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1726,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117452338</v>
+        <v>117451153</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>97753</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1738,45 +1747,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn (Kurlberget/Ramptjärn), Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516908</v>
+        <v>516596</v>
       </c>
       <c r="R12" t="n">
-        <v>6691891</v>
+        <v>6691840</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1832,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117451892</v>
+        <v>117452338</v>
       </c>
       <c r="B13" t="n">
         <v>97836</v>
@@ -1867,7 +1872,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1876,13 +1881,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516843</v>
+        <v>516908</v>
       </c>
       <c r="R13" t="n">
-        <v>6691994</v>
+        <v>6691891</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1938,10 +1943,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117451435</v>
+        <v>117452199</v>
       </c>
       <c r="B14" t="n">
-        <v>56499</v>
+        <v>97753</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1954,42 +1959,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn (Kurlberget/Ramptjärn), Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516620</v>
+        <v>516911</v>
       </c>
       <c r="R14" t="n">
-        <v>6691868</v>
+        <v>6691957</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 15917-2024 artfynd.xlsx
+++ b/artfynd/A 15917-2024 artfynd.xlsx
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117451830</v>
+        <v>117451125</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>91774</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,45 +908,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn (Kurlberget/Ramptjärn), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516845</v>
+        <v>516598</v>
       </c>
       <c r="R4" t="n">
-        <v>6691943</v>
+        <v>6691837</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,6 +972,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,7 +1006,7 @@
         <v>117452372</v>
       </c>
       <c r="B5" t="n">
-        <v>97753</v>
+        <v>97755</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117451892</v>
+        <v>117451153</v>
       </c>
       <c r="B6" t="n">
-        <v>97836</v>
+        <v>97755</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,42 +1117,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn (Kurlberget/Ramptjärn), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516843</v>
+        <v>516596</v>
       </c>
       <c r="R6" t="n">
-        <v>6691994</v>
+        <v>6691840</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1210,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117452042</v>
+        <v>117451830</v>
       </c>
       <c r="B7" t="n">
-        <v>97753</v>
+        <v>97838</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,41 +1219,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn (Kurlberget/Ramptjärn), Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516837</v>
+        <v>516845</v>
       </c>
       <c r="R7" t="n">
-        <v>6691989</v>
+        <v>6691943</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117451435</v>
+        <v>117451335</v>
       </c>
       <c r="B8" t="n">
-        <v>56499</v>
+        <v>78516</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,46 +1325,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn (Kurlberget/Ramptjärn), Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516620</v>
+        <v>516633</v>
       </c>
       <c r="R8" t="n">
-        <v>6691868</v>
+        <v>6691860</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1419,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117451335</v>
+        <v>117452338</v>
       </c>
       <c r="B9" t="n">
-        <v>78514</v>
+        <v>97838</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,38 +1427,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn (Kurlberget/Ramptjärn), Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516633</v>
+        <v>516908</v>
       </c>
       <c r="R9" t="n">
-        <v>6691860</v>
+        <v>6691891</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117451125</v>
+        <v>117452199</v>
       </c>
       <c r="B10" t="n">
-        <v>91772</v>
+        <v>97755</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,13 +1561,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516598</v>
+        <v>516911</v>
       </c>
       <c r="R10" t="n">
-        <v>6691837</v>
+        <v>6691957</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1597,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117451535</v>
+        <v>117452042</v>
       </c>
       <c r="B11" t="n">
-        <v>56499</v>
+        <v>97755</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,42 +1639,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn (Kurlberget/Ramptjärn), Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516613</v>
+        <v>516837</v>
       </c>
       <c r="R11" t="n">
-        <v>6691900</v>
+        <v>6691989</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1735,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117451153</v>
+        <v>117451535</v>
       </c>
       <c r="B12" t="n">
-        <v>97753</v>
+        <v>56500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,37 +1741,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn (Kurlberget/Ramptjärn), Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516596</v>
+        <v>516613</v>
       </c>
       <c r="R12" t="n">
-        <v>6691840</v>
+        <v>6691900</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1837,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117452338</v>
+        <v>117451892</v>
       </c>
       <c r="B13" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,7 +1867,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1881,13 +1876,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516908</v>
+        <v>516843</v>
       </c>
       <c r="R13" t="n">
-        <v>6691891</v>
+        <v>6691994</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1943,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117452199</v>
+        <v>117451435</v>
       </c>
       <c r="B14" t="n">
-        <v>97753</v>
+        <v>56500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,37 +1954,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn (Kurlberget/Ramptjärn), Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516911</v>
+        <v>516620</v>
       </c>
       <c r="R14" t="n">
-        <v>6691957</v>
+        <v>6691868</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
